--- a/public/dl/STEPIN_Tournament_Ops_Templates.xlsx
+++ b/public/dl/STEPIN_Tournament_Ops_Templates.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MC 큐시트" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="중계 장비 체크" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D-day 일정" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="중계 장비 체크" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D-day 일정" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,345 +459,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>STEPIN 대회 MC 큐시트</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>시간은 예시입니다. 대회별로 수정해 사용하세요. ★ 표시 멘트는 반드시 전달합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>시작</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>종료</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>소요(분)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>필수 멘트 (★)</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>OBS 장면</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>담당</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="C4" s="4">
-        <f>ROUND((TIMEVALUE(B4)-TIMEVALUE(A4))*1440,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>개막 · 선수 등록</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>오프닝 멘트, STEPIN 소개 ★</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>대기 화면</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>MC · 스태프</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C5" s="4">
-        <f>ROUND((TIMEVALUE(B5)-TIMEVALUE(A5))*1440,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>연습 시간</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>AI 채점 방식 ★, 송리스트 안내</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>대기 / 하이라이트</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>MC</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C6" s="4">
-        <f>ROUND((TIMEVALUE(B6)-TIMEVALUE(A6))*1440,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>32강 (16매치)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>대회 방식 ★, 선수 소개, 응원 유도</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>MC · 레퍼리</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C7" s="4">
-        <f>ROUND((TIMEVALUE(B7)-TIMEVALUE(A7))*1440,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>16강 · 8강</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>선수 스토리, 앱 소개 ★★★</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>경기 / 대진표</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>MC</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C8" s="4">
-        <f>ROUND((TIMEVALUE(B8)-TIMEVALUE(A8))*1440,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>4강 · 3-4위전 · 결승</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>결승 멘트</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>MC · 레퍼리</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C9" s="4">
-        <f>ROUND((TIMEVALUE(B9)-TIMEVALUE(A9))*1440,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>TOP3 인터뷰 · 기념 촬영</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>인터뷰 질문 3개</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>카메라 풀</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>MC · 촬영</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="C10" s="4">
-        <f>ROUND((TIMEVALUE(B10)-TIMEVALUE(A10))*1440,0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>시상 · 폐막</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>다음 대회 · 앱 대회 안내</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>결과 화면</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>MC</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -857,7 +517,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>아케이드 (STANDARD/WIDE/PORTABLE)</t>
+          <t>아케이드 (STANDARD/WIDE)</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -1457,7 +1117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/public/dl/STEPIN_Tournament_Ops_Templates.xlsx
+++ b/public/dl/STEPIN_Tournament_Ops_Templates.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,10 @@
     </font>
     <font>
       <name val="Malgun Gothic"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -84,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -93,6 +97,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,7 +474,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +484,13 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>중계 형태 (웹사이트 ‘방송 · 중계 셋팅 가이드’와 동일): TYPE 1 체험존 · 현장 랭킹전(중계 없음)  |  TYPE 2 현장 중계(관중용 대형 화면)  |  TYPE 3 녹화 · 현장 스케치  |  TYPE 4 라이브 송출(스트리밍 · 방송사)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -505,7 +519,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>필요 형태</t>
+          <t>필요 중계 형태</t>
         </is>
       </c>
     </row>
@@ -531,7 +545,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>TYPE 1~4</t>
+          <t>전체 형태 (TYPE 1~4)</t>
         </is>
       </c>
     </row>
@@ -557,7 +571,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -583,7 +597,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -609,7 +623,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>TYPE 4</t>
+          <t>라이브 송출 (TYPE 4)</t>
         </is>
       </c>
     </row>
@@ -635,7 +649,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -661,7 +675,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -687,7 +701,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>TYPE 3~4</t>
+          <t>녹화 · 라이브 송출 (TYPE 3~4)</t>
         </is>
       </c>
     </row>
@@ -713,7 +727,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>TYPE 4</t>
+          <t>라이브 송출 (TYPE 4)</t>
         </is>
       </c>
     </row>
@@ -739,7 +753,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -765,7 +779,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -791,7 +805,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -817,7 +831,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>TYPE 1~4</t>
+          <t>전체 형태 (TYPE 1~4)</t>
         </is>
       </c>
     </row>
@@ -843,7 +857,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>TYPE 1~4</t>
+          <t>전체 형태 (TYPE 1~4)</t>
         </is>
       </c>
     </row>
@@ -869,7 +883,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>TYPE 4</t>
+          <t>라이브 송출 (TYPE 4)</t>
         </is>
       </c>
     </row>
@@ -895,7 +909,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -921,7 +935,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -947,7 +961,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -973,7 +987,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -999,7 +1013,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>저조도 · TYPE 2~4</t>
+          <t>저조도 시 · 현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1039,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>TYPE 1~4</t>
+          <t>전체 형태 (TYPE 1~4)</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1065,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>TYPE 2~4</t>
+          <t>현장 중계 · 녹화 · 라이브 송출 (TYPE 2~4)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1091,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>TYPE 1~4</t>
+          <t>전체 형태 (TYPE 1~4)</t>
         </is>
       </c>
     </row>
@@ -1103,11 +1117,14 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>TYPE 1~4</t>
+          <t>전체 형태 (TYPE 1~4)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D4:D26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"O,X"</formula1>
